--- a/e2e/expectedData/sub_Daftar_Transfer_Potongan.xlsx
+++ b/e2e/expectedData/sub_Daftar_Transfer_Potongan.xlsx
@@ -50,7 +50,7 @@
     <t>No Data Available</t>
   </si>
   <si>
-    <t>DILI, 26 August 2026</t>
+    <t>DILI, 09 September 2026</t>
   </si>
   <si>
     <t>Human Resource</t>

--- a/e2e/expectedData/sub_Daftar_Transfer_Potongan.xlsx
+++ b/e2e/expectedData/sub_Daftar_Transfer_Potongan.xlsx
@@ -50,7 +50,7 @@
     <t>No Data Available</t>
   </si>
   <si>
-    <t>DILI, 09 September 2026</t>
+    <t>DILI, 10 September 2026</t>
   </si>
   <si>
     <t>Human Resource</t>
